--- a/products/Pricelist.xlsx
+++ b/products/Pricelist.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\shaham\projects\exc-site\products\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{97548D4A-669B-4BB9-9439-2C82DB22B1FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEAE2511-6111-4F04-9105-7BA99DFCBD1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="23415" yWindow="1050" windowWidth="38400" windowHeight="21150" xr2:uid="{E91AE6F1-DA7E-470B-920F-AEC7A60413FB}"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="38400" windowHeight="21150" xr2:uid="{E91AE6F1-DA7E-470B-920F-AEC7A60413FB}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>Model</t>
   </si>
@@ -46,6 +46,21 @@
   </si>
   <si>
     <t>OT16</t>
+  </si>
+  <si>
+    <t>C29 Lite</t>
+  </si>
+  <si>
+    <t>W77</t>
+  </si>
+  <si>
+    <t>OT08Pro</t>
+  </si>
+  <si>
+    <t>C29L</t>
+  </si>
+  <si>
+    <t>C29L Doppelt-Batterien</t>
   </si>
 </sst>
 </file>
@@ -401,9 +416,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC8964C2-A6D5-47BA-8376-C391B8440685}">
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="1" max="1" width="22" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -455,6 +471,46 @@
         <v>729</v>
       </c>
     </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" s="1">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" s="1">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" s="1">
+        <v>1429</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10" s="1">
+        <v>859</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11" s="1">
+        <v>1049</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/products/Pricelist.xlsx
+++ b/products/Pricelist.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\shaham\projects\exc-site\products\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEAE2511-6111-4F04-9105-7BA99DFCBD1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFFC53D7-7170-445E-A4AC-A9BB25E68D29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="390" yWindow="390" windowWidth="38400" windowHeight="21150" xr2:uid="{E91AE6F1-DA7E-470B-920F-AEC7A60413FB}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t>Model</t>
   </si>
@@ -61,6 +61,9 @@
   </si>
   <si>
     <t>C29L Doppelt-Batterien</t>
+  </si>
+  <si>
+    <t>F20</t>
   </si>
 </sst>
 </file>
@@ -416,7 +419,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC8964C2-A6D5-47BA-8376-C391B8440685}">
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22" bestFit="1" customWidth="1"/>
@@ -511,6 +514,14 @@
         <v>1049</v>
       </c>
     </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>12</v>
+      </c>
+      <c r="B12" s="1">
+        <v>1169</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/products/Pricelist.xlsx
+++ b/products/Pricelist.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\shaham\projects\exc-site\products\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFFC53D7-7170-445E-A4AC-A9BB25E68D29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCA99188-F8BF-4F6C-95A1-7C5675182608}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="390" yWindow="390" windowWidth="38400" windowHeight="21150" xr2:uid="{E91AE6F1-DA7E-470B-920F-AEC7A60413FB}"/>
+    <workbookView xWindow="23595" yWindow="2055" windowWidth="38400" windowHeight="21150" xr2:uid="{E91AE6F1-DA7E-470B-920F-AEC7A60413FB}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t>Model</t>
   </si>
@@ -33,9 +33,6 @@
     <t>Price</t>
   </si>
   <si>
-    <t>C29K</t>
-  </si>
-  <si>
     <t>OT01</t>
   </si>
   <si>
@@ -64,6 +61,12 @@
   </si>
   <si>
     <t>F20</t>
+  </si>
+  <si>
+    <t>C29K Doppelbatterie</t>
+  </si>
+  <si>
+    <t>F26Lite</t>
   </si>
 </sst>
 </file>
@@ -419,7 +422,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC8964C2-A6D5-47BA-8376-C391B8440685}">
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22" bestFit="1" customWidth="1"/>
@@ -436,7 +439,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="B2" s="1">
         <v>1199</v>
@@ -444,7 +447,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B3" s="1">
         <v>1089</v>
@@ -452,7 +455,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B4" s="1">
         <v>599</v>
@@ -460,7 +463,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B5" s="1">
         <v>729</v>
@@ -468,7 +471,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B6" s="1">
         <v>729</v>
@@ -476,7 +479,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B7" s="1">
         <v>749</v>
@@ -484,7 +487,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B8" s="1">
         <v>999</v>
@@ -492,7 +495,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B9" s="1">
         <v>1429</v>
@@ -500,7 +503,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B10" s="1">
         <v>859</v>
@@ -508,7 +511,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B11" s="1">
         <v>1049</v>
@@ -516,10 +519,18 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B12" s="1">
         <v>1169</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>13</v>
+      </c>
+      <c r="B13" s="1">
+        <v>1149</v>
       </c>
     </row>
   </sheetData>

--- a/products/Pricelist.xlsx
+++ b/products/Pricelist.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\shaham\projects\exc-site\products\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCA99188-F8BF-4F6C-95A1-7C5675182608}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9D86939-A502-4E14-8FF5-9C5912F18463}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="23595" yWindow="2055" windowWidth="38400" windowHeight="21150" xr2:uid="{E91AE6F1-DA7E-470B-920F-AEC7A60413FB}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <t>Model</t>
   </si>
@@ -67,6 +67,12 @@
   </si>
   <si>
     <t>F26Lite</t>
+  </si>
+  <si>
+    <t>N26</t>
+  </si>
+  <si>
+    <t>S26 Pro</t>
   </si>
 </sst>
 </file>
@@ -422,7 +428,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC8964C2-A6D5-47BA-8376-C391B8440685}">
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22" bestFit="1" customWidth="1"/>
@@ -533,6 +539,22 @@
         <v>1149</v>
       </c>
     </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14" s="1">
+        <v>1299</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>15</v>
+      </c>
+      <c r="B15" s="1">
+        <v>1299</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/products/Pricelist.xlsx
+++ b/products/Pricelist.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\shaham\projects\exc-site\products\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9D86939-A502-4E14-8FF5-9C5912F18463}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59938362-752F-4067-A658-A2734442C6AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="23595" yWindow="2055" windowWidth="38400" windowHeight="21150" xr2:uid="{E91AE6F1-DA7E-470B-920F-AEC7A60413FB}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
   <si>
     <t>Model</t>
   </si>
@@ -73,6 +73,9 @@
   </si>
   <si>
     <t>S26 Pro</t>
+  </si>
+  <si>
+    <t>E26</t>
   </si>
 </sst>
 </file>
@@ -428,7 +431,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC8964C2-A6D5-47BA-8376-C391B8440685}">
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22" bestFit="1" customWidth="1"/>
@@ -555,6 +558,14 @@
         <v>1299</v>
       </c>
     </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>16</v>
+      </c>
+      <c r="B16" s="1">
+        <v>1999</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/products/Pricelist.xlsx
+++ b/products/Pricelist.xlsx
@@ -1,102 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
-  <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\shaham\projects\exc-site\products\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59938362-752F-4067-A658-A2734442C6AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="23595" yWindow="2055" windowWidth="38400" windowHeight="21150" xr2:uid="{E91AE6F1-DA7E-470B-920F-AEC7A60413FB}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="23595" yWindow="2055" windowWidth="38400" windowHeight="21150" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="181029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
-  <si>
-    <t>Model</t>
-  </si>
-  <si>
-    <t>Price</t>
-  </si>
-  <si>
-    <t>OT01</t>
-  </si>
-  <si>
-    <t>OT02</t>
-  </si>
-  <si>
-    <t>OT12</t>
-  </si>
-  <si>
-    <t>OT16</t>
-  </si>
-  <si>
-    <t>C29 Lite</t>
-  </si>
-  <si>
-    <t>W77</t>
-  </si>
-  <si>
-    <t>OT08Pro</t>
-  </si>
-  <si>
-    <t>C29L</t>
-  </si>
-  <si>
-    <t>C29L Doppelt-Batterien</t>
-  </si>
-  <si>
-    <t>F20</t>
-  </si>
-  <si>
-    <t>C29K Doppelbatterie</t>
-  </si>
-  <si>
-    <t>F26Lite</t>
-  </si>
-  <si>
-    <t>N26</t>
-  </si>
-  <si>
-    <t>S26 Pro</t>
-  </si>
-  <si>
-    <t>E26</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="_([$€-2]\ * #,##0_);_([$€-2]\ * \(#,##0\);_([$€-2]\ * &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -115,22 +48,81 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -430,139 +422,197 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC8964C2-A6D5-47BA-8376-C391B8440685}">
-  <dimension ref="A1:B16"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="22" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11" style="1" bestFit="1" customWidth="1"/>
+    <col width="22" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="11" bestFit="1" customWidth="1" style="1" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B2" s="1">
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Price</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>C29K Doppelbatterie</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="n">
         <v>1199</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="1">
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>OT01</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="n">
         <v>1089</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" s="1">
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>OT02</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="n">
         <v>599</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" s="1">
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>OT12</t>
+        </is>
+      </c>
+      <c r="B5" s="1" t="n">
         <v>729</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6" s="1">
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>OT16</t>
+        </is>
+      </c>
+      <c r="B6" s="1" t="n">
         <v>729</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7" s="1">
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>C29 Lite</t>
+        </is>
+      </c>
+      <c r="B7" s="1" t="n">
         <v>749</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>7</v>
-      </c>
-      <c r="B8" s="1">
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>W77</t>
+        </is>
+      </c>
+      <c r="B8" s="1" t="n">
         <v>999</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>8</v>
-      </c>
-      <c r="B9" s="1">
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>OT08Pro</t>
+        </is>
+      </c>
+      <c r="B9" s="1" t="n">
         <v>1429</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>9</v>
-      </c>
-      <c r="B10" s="1">
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>C29L</t>
+        </is>
+      </c>
+      <c r="B10" s="1" t="n">
         <v>859</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>10</v>
-      </c>
-      <c r="B11" s="1">
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>C29L Doppelt-Batterien</t>
+        </is>
+      </c>
+      <c r="B11" s="1" t="n">
         <v>1049</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>11</v>
-      </c>
-      <c r="B12" s="1">
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>C29Pro</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>799</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>C29Pro Doppelt-Batterien</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>F20</t>
+        </is>
+      </c>
+      <c r="B14" s="1" t="n">
         <v>1169</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>13</v>
-      </c>
-      <c r="B13" s="1">
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>F26Lite</t>
+        </is>
+      </c>
+      <c r="B15" s="1" t="n">
         <v>1149</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>14</v>
-      </c>
-      <c r="B14" s="1">
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>N26</t>
+        </is>
+      </c>
+      <c r="B16" s="1" t="n">
         <v>1299</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>15</v>
-      </c>
-      <c r="B15" s="1">
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>S26 Pro</t>
+        </is>
+      </c>
+      <c r="B17" s="1" t="n">
         <v>1299</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>16</v>
-      </c>
-      <c r="B16" s="1">
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>E26</t>
+        </is>
+      </c>
+      <c r="B18" s="1" t="n">
         <v>1999</v>
       </c>
     </row>

--- a/products/Pricelist.xlsx
+++ b/products/Pricelist.xlsx
@@ -1,35 +1,112 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <workbookPr defaultThemeVersion="166925"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\shaham\projects\exc-site\products\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3E0028A-E403-48B1-853A-A9FBAD58129C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="23595" yWindow="2055" windowWidth="38400" windowHeight="21150" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="37440" yWindow="2520" windowWidth="38400" windowHeight="21150" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="181029" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
+  <si>
+    <t>Model</t>
+  </si>
+  <si>
+    <t>Price</t>
+  </si>
+  <si>
+    <t>C29K Doppelbatterie</t>
+  </si>
+  <si>
+    <t>OT01</t>
+  </si>
+  <si>
+    <t>OT02</t>
+  </si>
+  <si>
+    <t>OT12</t>
+  </si>
+  <si>
+    <t>OT16</t>
+  </si>
+  <si>
+    <t>C29 Lite</t>
+  </si>
+  <si>
+    <t>W77</t>
+  </si>
+  <si>
+    <t>OT08Pro</t>
+  </si>
+  <si>
+    <t>C29L</t>
+  </si>
+  <si>
+    <t>C29L Doppelt-Batterien</t>
+  </si>
+  <si>
+    <t>C29Pro</t>
+  </si>
+  <si>
+    <t>C29Pro Doppelt-Batterien</t>
+  </si>
+  <si>
+    <t>F20</t>
+  </si>
+  <si>
+    <t>F26Lite</t>
+  </si>
+  <si>
+    <t>N26</t>
+  </si>
+  <si>
+    <t>S26 Pro</t>
+  </si>
+  <si>
+    <t>E26</t>
+  </si>
+  <si>
+    <t>Literider</t>
+  </si>
+  <si>
+    <t>MX10</t>
+  </si>
+  <si>
+    <t>Smart30</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="_([$€-2]\ * #,##0_);_([$€-2]\ * \(#,##0\);_([$€-2]\ * &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -48,81 +125,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -422,198 +440,180 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B18"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:B21"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col width="22" bestFit="1" customWidth="1" min="1" max="1"/>
-    <col width="11" bestFit="1" customWidth="1" style="1" min="2" max="2"/>
+    <col min="1" max="1" width="22" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Model</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Price</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>C29K Doppelbatterie</t>
-        </is>
-      </c>
-      <c r="B2" s="1" t="n">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="1">
         <v>1199</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>OT01</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="n">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="1">
         <v>1089</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>OT02</t>
-        </is>
-      </c>
-      <c r="B4" s="1" t="n">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="1">
         <v>599</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>OT12</t>
-        </is>
-      </c>
-      <c r="B5" s="1" t="n">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="1">
         <v>729</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>OT16</t>
-        </is>
-      </c>
-      <c r="B6" s="1" t="n">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="1">
         <v>729</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>C29 Lite</t>
-        </is>
-      </c>
-      <c r="B7" s="1" t="n">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" s="1">
         <v>749</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>W77</t>
-        </is>
-      </c>
-      <c r="B8" s="1" t="n">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" s="1">
         <v>999</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>OT08Pro</t>
-        </is>
-      </c>
-      <c r="B9" s="1" t="n">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" s="1">
         <v>1429</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>C29L</t>
-        </is>
-      </c>
-      <c r="B10" s="1" t="n">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10" s="1">
         <v>859</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>C29L Doppelt-Batterien</t>
-        </is>
-      </c>
-      <c r="B11" s="1" t="n">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11" s="1">
         <v>1049</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>C29Pro</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>12</v>
+      </c>
+      <c r="B12">
         <v>799</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>C29Pro Doppelt-Batterien</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>13</v>
+      </c>
+      <c r="B13">
         <v>1039</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>F20</t>
-        </is>
-      </c>
-      <c r="B14" s="1" t="n">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14" s="1">
         <v>1169</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>F26Lite</t>
-        </is>
-      </c>
-      <c r="B15" s="1" t="n">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>15</v>
+      </c>
+      <c r="B15" s="1">
         <v>1149</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>N26</t>
-        </is>
-      </c>
-      <c r="B16" s="1" t="n">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>16</v>
+      </c>
+      <c r="B16" s="1">
         <v>1299</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>S26 Pro</t>
-        </is>
-      </c>
-      <c r="B17" s="1" t="n">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>17</v>
+      </c>
+      <c r="B17" s="1">
         <v>1299</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>E26</t>
-        </is>
-      </c>
-      <c r="B18" s="1" t="n">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>18</v>
+      </c>
+      <c r="B18" s="1">
         <v>1999</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>19</v>
+      </c>
+      <c r="B19" s="1">
+        <v>1029</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>20</v>
+      </c>
+      <c r="B20" s="1">
+        <v>939</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>21</v>
+      </c>
+      <c r="B21" s="1">
+        <v>1059</v>
       </c>
     </row>
   </sheetData>

--- a/products/Pricelist.xlsx
+++ b/products/Pricelist.xlsx
@@ -1,112 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
-  <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\shaham\projects\exc-site\products\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3E0028A-E403-48B1-853A-A9FBAD58129C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="37440" yWindow="2520" windowWidth="38400" windowHeight="21150" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="37440" yWindow="2520" windowWidth="38400" windowHeight="21150" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
-  <si>
-    <t>Model</t>
-  </si>
-  <si>
-    <t>Price</t>
-  </si>
-  <si>
-    <t>C29K Doppelbatterie</t>
-  </si>
-  <si>
-    <t>OT01</t>
-  </si>
-  <si>
-    <t>OT02</t>
-  </si>
-  <si>
-    <t>OT12</t>
-  </si>
-  <si>
-    <t>OT16</t>
-  </si>
-  <si>
-    <t>C29 Lite</t>
-  </si>
-  <si>
-    <t>W77</t>
-  </si>
-  <si>
-    <t>OT08Pro</t>
-  </si>
-  <si>
-    <t>C29L</t>
-  </si>
-  <si>
-    <t>C29L Doppelt-Batterien</t>
-  </si>
-  <si>
-    <t>C29Pro</t>
-  </si>
-  <si>
-    <t>C29Pro Doppelt-Batterien</t>
-  </si>
-  <si>
-    <t>F20</t>
-  </si>
-  <si>
-    <t>F26Lite</t>
-  </si>
-  <si>
-    <t>N26</t>
-  </si>
-  <si>
-    <t>S26 Pro</t>
-  </si>
-  <si>
-    <t>E26</t>
-  </si>
-  <si>
-    <t>Literider</t>
-  </si>
-  <si>
-    <t>MX10</t>
-  </si>
-  <si>
-    <t>Smart30</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="_([$€-2]\ * #,##0_);_([$€-2]\ * \(#,##0\);_([$€-2]\ * &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -125,22 +48,81 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -440,180 +422,238 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B21"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="22" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11" style="1" bestFit="1" customWidth="1"/>
+    <col width="22" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="11" bestFit="1" customWidth="1" style="1" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="1">
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Price</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>C29K Doppelbatterie</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="n">
         <v>1199</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="1">
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>OT01</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="n">
         <v>1089</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" s="1">
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>OT02</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="n">
         <v>599</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5" s="1">
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>OT12</t>
+        </is>
+      </c>
+      <c r="B5" s="1" t="n">
         <v>729</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6" s="1">
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>OT16</t>
+        </is>
+      </c>
+      <c r="B6" s="1" t="n">
         <v>729</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>7</v>
-      </c>
-      <c r="B7" s="1">
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>C29 Lite</t>
+        </is>
+      </c>
+      <c r="B7" s="1" t="n">
         <v>749</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8" s="1">
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>W77</t>
+        </is>
+      </c>
+      <c r="B8" s="1" t="n">
         <v>999</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>9</v>
-      </c>
-      <c r="B9" s="1">
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>OT08Pro</t>
+        </is>
+      </c>
+      <c r="B9" s="1" t="n">
         <v>1429</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>10</v>
-      </c>
-      <c r="B10" s="1">
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>C29L</t>
+        </is>
+      </c>
+      <c r="B10" s="1" t="n">
         <v>859</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>11</v>
-      </c>
-      <c r="B11" s="1">
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>C29L Doppelt-Batterien</t>
+        </is>
+      </c>
+      <c r="B11" s="1" t="n">
         <v>1049</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>12</v>
-      </c>
-      <c r="B12">
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>C29Pro</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
         <v>799</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>13</v>
-      </c>
-      <c r="B13">
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>C29Pro Doppelt-Batterien</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
         <v>1039</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>14</v>
-      </c>
-      <c r="B14" s="1">
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>F20</t>
+        </is>
+      </c>
+      <c r="B14" s="1" t="n">
         <v>1169</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>15</v>
-      </c>
-      <c r="B15" s="1">
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>F26Lite</t>
+        </is>
+      </c>
+      <c r="B15" s="1" t="n">
         <v>1149</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>16</v>
-      </c>
-      <c r="B16" s="1">
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>N26</t>
+        </is>
+      </c>
+      <c r="B16" s="1" t="n">
         <v>1299</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>17</v>
-      </c>
-      <c r="B17" s="1">
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>S26 Pro</t>
+        </is>
+      </c>
+      <c r="B17" s="1" t="n">
         <v>1299</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>18</v>
-      </c>
-      <c r="B18" s="1">
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>E26</t>
+        </is>
+      </c>
+      <c r="B18" s="1" t="n">
         <v>1999</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>19</v>
-      </c>
-      <c r="B19" s="1">
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Literider</t>
+        </is>
+      </c>
+      <c r="B19" s="1" t="n">
         <v>1029</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>20</v>
-      </c>
-      <c r="B20" s="1">
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>MX10</t>
+        </is>
+      </c>
+      <c r="B20" s="1" t="n">
         <v>939</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>21</v>
-      </c>
-      <c r="B21" s="1">
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Smart30</t>
+        </is>
+      </c>
+      <c r="B21" s="1" t="n">
         <v>1059</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Urbaun7</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>809</v>
       </c>
     </row>
   </sheetData>

--- a/products/Pricelist.xlsx
+++ b/products/Pricelist.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B22"/>
+  <dimension ref="A1:B23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -649,11 +649,21 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Urbaun7</t>
+          <t>Urban7</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>809</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Polaris</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>779</v>
       </c>
     </row>
   </sheetData>

--- a/products/Pricelist.xlsx
+++ b/products/Pricelist.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B23"/>
+  <dimension ref="A1:B24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -666,6 +666,16 @@
         <v>779</v>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Camel</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>969</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/products/Pricelist.xlsx
+++ b/products/Pricelist.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B24"/>
+  <dimension ref="A1:B25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -676,6 +676,16 @@
         <v>969</v>
       </c>
     </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>OT02Pro</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>629</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/products/Pricelist.xlsx
+++ b/products/Pricelist.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B25"/>
+  <dimension ref="A1:B26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -686,6 +686,16 @@
         <v>629</v>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>OT05</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>1029</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/products/Pricelist.xlsx
+++ b/products/Pricelist.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B26"/>
+  <dimension ref="A1:B27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -696,6 +696,16 @@
         <v>1029</v>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>OT05 Pro</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>1149</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/products/Pricelist.xlsx
+++ b/products/Pricelist.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B27"/>
+  <dimension ref="A1:B28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -706,6 +706,16 @@
         <v>1149</v>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>E29</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>1359</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
